--- a/marketing_report/outputs/Grado_Pregrado/Bot_Deep_Dive/datos_bot_deep_dive.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Bot_Deep_Dive/datos_bot_deep_dive.xlsx
@@ -459,13 +459,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>704</v>
+        <v>543</v>
       </c>
       <c r="D2" t="n">
-        <v>4.26</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>19.48</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="4">
@@ -491,125 +491,125 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>28.57</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONTADOR PÚBLICO</t>
+          <t>ESCRIBANÍA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
-        <v>7.43</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LICENCIATURA EN RECURSOS HUMANOS</t>
+          <t>CONTADOR PÚBLICO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D6" t="n">
-        <v>8.85</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LICENCIATURA EN PSICOLOGÍA</t>
+          <t>LICENCIATURA EN RECURSOS HUMANOS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="D7" t="n">
-        <v>6.38</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LICENCIATURA EN HIGIENE Y SEGURIDAD EN EL TRABAJO</t>
+          <t>LICENCIATURA EN DISEÑO GRÁFICO</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>5.77</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LICENCIATURA EN CRIMINALÍSTICA</t>
+          <t>LICENCIATURA EN HIGIENE Y SEGURIDAD EN EL TRABAJO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D9" t="n">
-        <v>9.460000000000001</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LICENCIATURA EN DISEÑO GRÁFICO</t>
+          <t>LICENCIATURA EN PSICOLOGÍA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="D10" t="n">
-        <v>25.93</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DISEÑO INDUSTRIAL</t>
+          <t>INGENIERÍA EN INFORMÁTICA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>66.67</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1619</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="3">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1418</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="4">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>720</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="5">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -705,37 +705,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAFAYATE - SALTA</t>
+          <t>SANTIAGO DEL ESTERO - SANTIAGO DEL ESTERO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAPITAL FEDERAL - CABA</t>
+          <t>CAFAYATE - SALTA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DELEGACION CONCORDIA - ENTRE RÍOS</t>
+          <t>TARTAGAL - SALTA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1984</v>
+        <v>4231</v>
       </c>
       <c r="C2" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="3">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>984</v>
+        <v>2217</v>
       </c>
       <c r="C3" t="n">
-        <v>25.1</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="4">
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>824</v>
+        <v>1670</v>
       </c>
       <c r="C4" t="n">
-        <v>21.1</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="5">
@@ -815,10 +815,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>121</v>
+        <v>330</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pre Inscripción</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Grado_Pregrado/Bot_Deep_Dive/datos_bot_deep_dive.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Bot_Deep_Dive/datos_bot_deep_dive.xlsx
@@ -1,39 +1,149 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Top_Carreras" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sedes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Estados" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Top_Carreras" sheetId="1" r:id="rId1"/>
+    <sheet name="Sedes" sheetId="2" r:id="rId2"/>
+    <sheet name="Estados" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>Carrera</t>
+  </si>
+  <si>
+    <t>Inscriptos (Muestra)</t>
+  </si>
+  <si>
+    <t>Consultas (Muestra)</t>
+  </si>
+  <si>
+    <t>Tasa_%</t>
+  </si>
+  <si>
+    <t>ABOGACÍA</t>
+  </si>
+  <si>
+    <t>CIENCIAS VETERINARIAS</t>
+  </si>
+  <si>
+    <t>ARQUITECTURA</t>
+  </si>
+  <si>
+    <t>ESCRIBANÍA</t>
+  </si>
+  <si>
+    <t>CONTADOR PÚBLICO</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN RECURSOS HUMANOS</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN DISEÑO GRÁFICO</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN HIGIENE Y SEGURIDAD EN EL TRABAJO</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN PSICOLOGÍA</t>
+  </si>
+  <si>
+    <t>INGENIERÍA EN INFORMÁTICA</t>
+  </si>
+  <si>
+    <t>Sede</t>
+  </si>
+  <si>
+    <t>Leads</t>
+  </si>
+  <si>
+    <t>SALTA - CASTAÑARES PRESENCIAL</t>
+  </si>
+  <si>
+    <t>HOME</t>
+  </si>
+  <si>
+    <t>SALTA - DISTANCIA Modo 7</t>
+  </si>
+  <si>
+    <t>DELEGACIÓN SAN MIGUEL - BUENOS AIRES Modo 7</t>
+  </si>
+  <si>
+    <t>DELEGACION S S DE JUJUY - JUJUY</t>
+  </si>
+  <si>
+    <t>SALTA - ANEXO CENTRO</t>
+  </si>
+  <si>
+    <t>BUENOS AIRES - CABA</t>
+  </si>
+  <si>
+    <t>SANTIAGO DEL ESTERO - SANTIAGO DEL ESTERO</t>
+  </si>
+  <si>
+    <t>CAFAYATE - SALTA</t>
+  </si>
+  <si>
+    <t>TARTAGAL - SALTA</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Abierto</t>
+  </si>
+  <si>
+    <t>No interesado</t>
+  </si>
+  <si>
+    <t>Interesado</t>
+  </si>
+  <si>
+    <t>Solicitud creada</t>
+  </si>
+  <si>
+    <t>Pre Inscripción</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,93 +158,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -422,419 +474,339 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Carrera</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Inscriptos (Muestra)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Consultas (Muestra)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Tasa_%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ABOGACÍA</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>36</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>543</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>6.63</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CIENCIAS VETERINARIAS</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>20</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>68</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>29.41</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>15</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>31</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>48.39</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ESCRIBANÍA</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>13</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>110</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>11.82</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONTADOR PÚBLICO</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>12</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>103</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>11.65</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LICENCIATURA EN RECURSOS HUMANOS</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>10</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>88</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>11.36</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LICENCIATURA EN DISEÑO GRÁFICO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>19</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>47.37</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LICENCIATURA EN HIGIENE Y SEGURIDAD EN EL TRABAJO</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
         <v>9</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>127</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>7.09</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LICENCIATURA EN PSICOLOGÍA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
         <v>8</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>102</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>7.84</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INGENIERÍA EN INFORMÁTICA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
         <v>8</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>40</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sede</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Leads</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SALTA - CASTAÑARES PRESENCIAL</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
         <v>3828</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
         <v>2775</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SALTA - DISTANCIA Modo 7</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
         <v>1522</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DELEGACIÓN SAN MIGUEL - BUENOS AIRES Modo 7</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
         <v>104</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DELEGACION S S DE JUJUY - JUJUY</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
         <v>60</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SALTA - ANEXO CENTRO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
         <v>50</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BUENOS AIRES - CABA</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
         <v>38</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SANTIAGO DEL ESTERO - SANTIAGO DEL ESTERO</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
         <v>7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CAFAYATE - SALTA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
         <v>5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TARTAGAL - SALTA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Abierto</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2">
         <v>4231</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>50.1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>No interesado</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
         <v>2217</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>26.2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Interesado</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
         <v>1670</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>19.8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Solicitud creada</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
         <v>330</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>3.9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pre Inscripción</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/marketing_report/outputs/Grado_Pregrado/Bot_Deep_Dive/datos_bot_deep_dive.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Bot_Deep_Dive/datos_bot_deep_dive.xlsx
@@ -33,33 +33,33 @@
     <t>ABOGACÍA</t>
   </si>
   <si>
+    <t>ARQUITECTURA</t>
+  </si>
+  <si>
+    <t>CONTADOR PÚBLICO</t>
+  </si>
+  <si>
     <t>CIENCIAS VETERINARIAS</t>
   </si>
   <si>
-    <t>ARQUITECTURA</t>
+    <t>LICENCIATURA EN KINESIOLOGÍA Y FISIOTERAPIA</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN PSICOLOGÍA</t>
   </si>
   <si>
     <t>ESCRIBANÍA</t>
   </si>
   <si>
-    <t>CONTADOR PÚBLICO</t>
-  </si>
-  <si>
-    <t>LICENCIATURA EN RECURSOS HUMANOS</t>
-  </si>
-  <si>
-    <t>LICENCIATURA EN DISEÑO GRÁFICO</t>
-  </si>
-  <si>
     <t>LICENCIATURA EN HIGIENE Y SEGURIDAD EN EL TRABAJO</t>
   </si>
   <si>
-    <t>LICENCIATURA EN PSICOLOGÍA</t>
-  </si>
-  <si>
     <t>INGENIERÍA EN INFORMÁTICA</t>
   </si>
   <si>
+    <t>LICENCIATURA EN CRIMINALÍSTICA</t>
+  </si>
+  <si>
     <t>Sede</t>
   </si>
   <si>
@@ -75,10 +75,10 @@
     <t>SALTA - DISTANCIA Modo 7</t>
   </si>
   <si>
+    <t>DELEGACION S S DE JUJUY - JUJUY</t>
+  </si>
+  <si>
     <t>DELEGACIÓN SAN MIGUEL - BUENOS AIRES Modo 7</t>
-  </si>
-  <si>
-    <t>DELEGACION S S DE JUJUY - JUJUY</t>
   </si>
   <si>
     <t>SALTA - ANEXO CENTRO</t>
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="C2">
-        <v>543</v>
+        <v>1840</v>
       </c>
       <c r="D2">
-        <v>6.63</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C3">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="D3">
-        <v>29.41</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>364</v>
       </c>
       <c r="D4">
-        <v>48.39</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="D5">
-        <v>11.82</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="D6">
-        <v>11.65</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>88</v>
+        <v>363</v>
       </c>
       <c r="D7">
-        <v>11.36</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>305</v>
       </c>
       <c r="D8">
-        <v>47.37</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C9">
-        <v>127</v>
+        <v>392</v>
       </c>
       <c r="D9">
-        <v>7.09</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D10">
-        <v>7.84</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>10.22</v>
       </c>
     </row>
   </sheetData>
@@ -655,7 +655,7 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>3828</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -663,7 +663,7 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>2775</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>1522</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -679,7 +679,7 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>104</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -687,7 +687,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>60</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -695,7 +695,7 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -703,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -756,10 +756,10 @@
         <v>29</v>
       </c>
       <c r="B2">
-        <v>4231</v>
+        <v>4916</v>
       </c>
       <c r="C2">
-        <v>50.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -767,10 +767,10 @@
         <v>30</v>
       </c>
       <c r="B3">
-        <v>2217</v>
+        <v>2849</v>
       </c>
       <c r="C3">
-        <v>26.2</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -778,10 +778,10 @@
         <v>31</v>
       </c>
       <c r="B4">
-        <v>1670</v>
+        <v>2051</v>
       </c>
       <c r="C4">
-        <v>19.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -789,10 +789,10 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>330</v>
+        <v>427</v>
       </c>
       <c r="C5">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6" spans="1:3">
